--- a/partC/performance_test/results/Performance_test_data.xlsx
+++ b/partC/performance_test/results/Performance_test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boty2\Documents\429repo\ECSE429\partC\performance_test\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EE260E-F925-4D32-9D5F-D4B5E56B81AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5418E7-D3AB-4B71-8126-5CE8BCAD7C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{0FDACD7D-C75C-4684-9E02-769D6DDB9777}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="3" xr2:uid="{0FDACD7D-C75C-4684-9E02-769D6DDB9777}"/>
   </bookViews>
   <sheets>
     <sheet name="performance-2026-04-05T15-18-24" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,6 @@
     <sheet name="Projects" sheetId="4" r:id="rId3"/>
     <sheet name="Categories" sheetId="3" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">(TODOs!$B$2,TODOs!$B$5,TODOs!$B$8,TODOs!$B$11,TODOs!$B$14,TODOs!$B$17)</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">(TODOs!$B$3,TODOs!$B$6,TODOs!$B$9,TODOs!$B$12,TODOs!$B$15,TODOs!$B$18)</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">(TODOs!$B$4,TODOs!$B$7,TODOs!$B$10,TODOs!$B$13,TODOs!$B$16,TODOs!$B$19)</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">(TODOs!$G$2,TODOs!$G$5,TODOs!$G$8,TODOs!$G$11,TODOs!$G$14,TODOs!$G$17)</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">(TODOs!$G$3,TODOs!$G$6,TODOs!$G$9,TODOs!$G$12,TODOs!$G$15,TODOs!$G$18)</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">(TODOs!$G$4,TODOs!$G$7,TODOs!$G$4,TODOs!$G$7,TODOs!$G$10,TODOs!$G$13,TODOs!$G$16,TODOs!$G$19)</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -695,7 +687,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1081,7 +1073,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1410,7 +1402,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1802,7 +1794,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1938,7 +1930,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2136,7 +2128,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2522,7 +2514,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2851,7 +2843,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3368,7 +3360,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3566,7 +3558,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3952,7 +3944,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -4088,7 +4080,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -4251,7 +4243,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-CA"/>
-              <a:t>Free Memory vs N</a:t>
+              <a:t>Projects Free Memory vs N</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4669,7 +4661,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -4805,7 +4797,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -5003,7 +4995,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5389,7 +5381,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -5525,7 +5517,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -5723,7 +5715,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6109,7 +6101,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -6245,7 +6237,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -6443,7 +6435,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6829,7 +6821,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -6965,7 +6957,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-CA"/>
             </a:p>
           </c:txPr>
         </c:title>
